--- a/Excel/AchievementGroupConfig.xlsx
+++ b/Excel/AchievementGroupConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
   <si>
     <t>_id</t>
   </si>
@@ -114,6 +119,9 @@
   </si>
   <si>
     <t>神秘成就</t>
+  </si>
+  <si>
+    <t>困难彩蛋</t>
   </si>
 </sst>
 </file>
@@ -1078,7 +1086,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:E35"/>
+  <dimension ref="C3:E36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -1369,6 +1377,17 @@
         <v>28</v>
       </c>
       <c r="E35" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:5">
+      <c r="C36" s="3">
+        <v>503</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="3">
         <v>5</v>
       </c>
     </row>
